--- a/ESTADO_TRASTEROS.xlsx
+++ b/ESTADO_TRASTEROS.xlsx
@@ -890,7 +890,7 @@
         <v>12950</v>
       </c>
       <c r="H21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -994,7 +994,7 @@
         <v>10950</v>
       </c>
       <c r="H25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -2008,7 +2008,7 @@
         <v>12500</v>
       </c>
       <c r="H64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -3007,7 +3007,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H102" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H20 A65:H102 A64:G64 A22:H24 A21:G21 A26:H63 A25:G25" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>